--- a/cronograma_procesos.xlsx
+++ b/cronograma_procesos.xlsx
@@ -1481,7 +1481,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>15/10/2026 10:00 Hrs.</t>
+          <t>21/10/2026 10:00 Hrs.</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>20/10/2026 10:00 Hrs.</t>
+          <t>26/10/2026 10:00 Hrs.</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>20/10/2026 10:00 Hrs.</t>
+          <t>26/10/2026 10:00 Hrs.</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
@@ -3904,11 +3904,19 @@
       <c r="W43" t="inlineStr"/>
       <c r="X43" t="inlineStr">
         <is>
-          <t>ACTIVA</t>
-        </is>
-      </c>
-      <c r="Y43" t="inlineStr"/>
-      <c r="Z43" t="inlineStr"/>
+          <t>EN SEGUIMIENTO</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>Marcado desde dashboard</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>16/10/2026 17:45</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -5186,19 +5194,11 @@
       <c r="W58" t="inlineStr"/>
       <c r="X58" t="inlineStr">
         <is>
-          <t>EN SEGUIMIENTO</t>
-        </is>
-      </c>
-      <c r="Y58" t="inlineStr">
-        <is>
-          <t>Marcado desde dashboard</t>
-        </is>
-      </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>14/10/2026 21:17</t>
-        </is>
-      </c>
+          <t>ACTIVA</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr"/>
+      <c r="Z58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>07/10/2026 09:00 Hrs.</t>
+          <t>16/10/2026 09:00 Hrs.</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>15/10/2026 09:00 Hrs.</t>
+          <t>22/10/2026 09:00 Hrs.</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
@@ -5319,7 +5319,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>20/10/2026 09:00 Hrs.</t>
+          <t>27/10/2026 09:00 Hrs.</t>
         </is>
       </c>
       <c r="J60" t="inlineStr"/>

--- a/cronograma_procesos.xlsx
+++ b/cronograma_procesos.xlsx
@@ -1481,7 +1481,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>21/10/2026 10:00 Hrs.</t>
+          <t>15/10/2026 10:00 Hrs.</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>26/10/2026 10:00 Hrs.</t>
+          <t>20/10/2026 10:00 Hrs.</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>26/10/2026 10:00 Hrs.</t>
+          <t>20/10/2026 10:00 Hrs.</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
@@ -3904,19 +3904,11 @@
       <c r="W43" t="inlineStr"/>
       <c r="X43" t="inlineStr">
         <is>
-          <t>EN SEGUIMIENTO</t>
-        </is>
-      </c>
-      <c r="Y43" t="inlineStr">
-        <is>
-          <t>Marcado desde dashboard</t>
-        </is>
-      </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>16/10/2026 17:45</t>
-        </is>
-      </c>
+          <t>ACTIVA</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr"/>
+      <c r="Z43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -5194,11 +5186,19 @@
       <c r="W58" t="inlineStr"/>
       <c r="X58" t="inlineStr">
         <is>
-          <t>ACTIVA</t>
-        </is>
-      </c>
-      <c r="Y58" t="inlineStr"/>
-      <c r="Z58" t="inlineStr"/>
+          <t>EN SEGUIMIENTO</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>Marcado desde dashboard</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>14/10/2026 21:17</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>16/10/2026 09:00 Hrs.</t>
+          <t>07/10/2026 09:00 Hrs.</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>22/10/2026 09:00 Hrs.</t>
+          <t>15/10/2026 09:00 Hrs.</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
@@ -5319,7 +5319,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>27/10/2026 09:00 Hrs.</t>
+          <t>20/10/2026 09:00 Hrs.</t>
         </is>
       </c>
       <c r="J60" t="inlineStr"/>
@@ -6502,11 +6502,19 @@
       <c r="W74" t="inlineStr"/>
       <c r="X74" t="inlineStr">
         <is>
-          <t>ACTIVA</t>
-        </is>
-      </c>
-      <c r="Y74" t="inlineStr"/>
-      <c r="Z74" t="inlineStr"/>
+          <t>EN SEGUIMIENTO</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>Marcado desde dashboard</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>17/10/2026 08:46</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
